--- a/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-donor-order.xlsx
+++ b/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-donor-order.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$53</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="509">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T19:29:11+00:00</t>
+    <t>2026-09-03T14:51:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A profile representing a donor workup or collection order in the NMDP system. Orders include confirmatory typing (CT), infectious disease markers (IDM), and stem cell collection.</t>
+    <t>A profile representing a donor workup order in the NMDP system. For donors, the ordered item is always confirmatory typing. ServiceRequest.subject references the recipient Patient, and ServiceRequest.performer references the donor Patient.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -513,19 +513,19 @@
     <t>ClinicalStatement.identifier</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier:nmdpOrderId</t>
-  </si>
-  <si>
-    <t>nmdpOrderId</t>
-  </si>
-  <si>
-    <t>NMDP Order ID</t>
-  </si>
-  <si>
-    <t>The unique identifier assigned to this order by the NMDP system.</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:nmdpOrderId.id</t>
+    <t>ServiceRequest.identifier:matchsourceOrder</t>
+  </si>
+  <si>
+    <t>matchsourceOrder</t>
+  </si>
+  <si>
+    <t>MatchSource order number</t>
+  </si>
+  <si>
+    <t>The order number assigned by the NMDP MatchSource system. System: http://nmdp.org/identifier/matchsource-order</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:matchsourceOrder.id</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.id</t>
@@ -547,7 +547,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier:nmdpOrderId.extension</t>
+    <t>ServiceRequest.identifier:matchsourceOrder.extension</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.extension</t>
@@ -566,7 +566,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier:nmdpOrderId.use</t>
+    <t>ServiceRequest.identifier:matchsourceOrder.use</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.use</t>
@@ -599,7 +599,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier:nmdpOrderId.type</t>
+    <t>ServiceRequest.identifier:matchsourceOrder.type</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.type</t>
@@ -636,7 +636,7 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier:nmdpOrderId.system</t>
+    <t>ServiceRequest.identifier:matchsourceOrder.system</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.system</t>
@@ -654,7 +654,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://terminology.nmdp.org/identifier/order</t>
+    <t>http://nmdp.org/identifier/matchsource-order</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -669,7 +669,7 @@
     <t>II.root or Role.id.root</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier:nmdpOrderId.value</t>
+    <t>ServiceRequest.identifier:matchsourceOrder.value</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.value</t>
@@ -696,7 +696,7 @@
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier:nmdpOrderId.period</t>
+    <t>ServiceRequest.identifier:matchsourceOrder.period</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.period</t>
@@ -721,7 +721,7 @@
     <t>Role.effectiveTime or implied by context</t>
   </si>
   <si>
-    <t>ServiceRequest.identifier:nmdpOrderId.assigner</t>
+    <t>ServiceRequest.identifier:matchsourceOrder.assigner</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.assigner</t>
@@ -1027,10 +1027,10 @@
 </t>
   </si>
   <si>
-    <t>Type of order (CT, IDM, Collection, PBSC, Marrow)</t>
-  </si>
-  <si>
-    <t>A code that identifies a particular service (i.e., procedure, diagnostic investigation, or panel of investigations) that have been requested.</t>
+    <t>Type of order (e.g., confirmatory-typing)</t>
+  </si>
+  <si>
+    <t>The type of donor order. For donor orders this is always confirmatory typing (code: confirmatory-typing).</t>
   </si>
   <si>
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
@@ -1109,10 +1109,10 @@
 </t>
   </si>
   <si>
-    <t>The donor this order is for</t>
-  </si>
-  <si>
-    <t>The donor (NMDPDonorPatient) this order is for. Constrained to Patient references.</t>
+    <t>The recipient Patient this order is for</t>
+  </si>
+  <si>
+    <t>The recipient Patient (identified by RID) that this donor order is associated with.</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -1179,6 +1179,10 @@
     <t>The date/time at which the requested service should occur.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>Request.occurrence[x]</t>
   </si>
   <si>
@@ -1192,6 +1196,19 @@
   </si>
   <si>
     <t>Procedure.procedureSchedule</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x]:occurrenceDateTime</t>
+  </si>
+  <si>
+    <t>occurrenceDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Appointment date (CT draw appointment)</t>
   </si>
   <si>
     <t>ServiceRequest.asNeeded[x]</t>
@@ -1226,11 +1243,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>When the order was created</t>
+    <t>Order submitted date</t>
   </si>
   <si>
     <t>When the request transitioned to being actionable.</t>
@@ -1258,14 +1271,14 @@
 orderer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://fhir.nmdp.org/ig/donor-patient/StructureDefinition/nmdp-organization|Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
-    <t>Organization or practitioner who requested this order</t>
-  </si>
-  <si>
-    <t>The transplant center or practitioner who initiated the donor workup or collection order.</t>
+    <t>Who/what is requesting service</t>
+  </si>
+  <si>
+    <t>The individual who initiated the request and has responsibility for its activation.</t>
   </si>
   <si>
     <t>This not the dispatcher, but rather who is the authorizer.  This element is not intended to handle delegation which would generally be managed through the Provenance resource.</t>
@@ -1327,14 +1340,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://fhir.nmdp.org/ig/donor-patient/StructureDefinition/nmdp-organization)
-</t>
-  </si>
-  <si>
-    <t>Organization performing the order</t>
-  </si>
-  <si>
-    <t>The donor center, collection center, or lab performing this order.</t>
+    <t>The donor Patient performing this order</t>
+  </si>
+  <si>
+    <t>The donor Patient (identified by GRID) who will undergo the ordered procedure.</t>
   </si>
   <si>
     <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
@@ -1908,12 +1917,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO52"/>
+  <dimension ref="A1:AO53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.91015625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.15234375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="30.62109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1921,7 +1930,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.46875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="93.98828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -5488,7 +5497,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>90</v>
@@ -6127,16 +6136,14 @@
         <v>81</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="AC36" s="2"/>
       <c r="AD36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>369</v>
@@ -6154,31 +6161,33 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="D37" t="s" s="2">
-        <v>81</v>
+        <v>370</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6188,7 +6197,7 @@
         <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>81</v>
@@ -6197,13 +6206,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6230,13 +6239,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>383</v>
+        <v>81</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>384</v>
+        <v>81</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6254,7 +6263,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6269,41 +6278,41 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>81</v>
+        <v>375</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>81</v>
+        <v>376</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>81</v>
+        <v>378</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>81</v>
@@ -6312,13 +6321,13 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6345,13 +6354,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6369,7 +6378,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6384,35 +6393,35 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>395</v>
+        <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>90</v>
@@ -6427,17 +6436,15 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6486,7 +6493,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6501,31 +6508,31 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6544,16 +6551,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>189</v>
+        <v>403</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6579,13 +6586,13 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -6603,7 +6610,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6618,41 +6625,41 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>81</v>
+        <v>411</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>81</v>
@@ -6661,16 +6668,16 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>421</v>
+        <v>189</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6696,13 +6703,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>81</v>
+        <v>417</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6720,13 +6727,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6735,31 +6742,31 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>81</v>
+        <v>424</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6769,7 +6776,7 @@
         <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>81</v>
@@ -6778,15 +6785,17 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>189</v>
+        <v>351</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6811,13 +6820,13 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>432</v>
+        <v>81</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -6835,7 +6844,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6850,16 +6859,16 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>81</v>
+        <v>428</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>81</v>
+        <v>429</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -6867,10 +6876,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6893,13 +6902,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>435</v>
+        <v>189</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6926,13 +6935,13 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>81</v>
+        <v>434</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -6950,7 +6959,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6971,10 +6980,10 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
@@ -6982,10 +6991,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7008,17 +7017,15 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>189</v>
+        <v>438</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>441</v>
-      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7043,13 +7050,13 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>443</v>
+        <v>81</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7067,7 +7074,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7082,16 +7089,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
@@ -7099,10 +7106,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7125,16 +7132,16 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>449</v>
+        <v>189</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7160,13 +7167,13 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>81</v>
+        <v>446</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -7184,7 +7191,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7199,16 +7206,16 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7216,10 +7223,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7239,18 +7246,20 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7299,7 +7308,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7314,16 +7323,16 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7331,14 +7340,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>464</v>
+        <v>81</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7357,17 +7366,15 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7416,7 +7423,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7431,13 +7438,13 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7448,14 +7455,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>81</v>
+        <v>467</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7471,19 +7478,19 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7533,7 +7540,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7548,13 +7555,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>81</v>
+        <v>472</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7565,14 +7572,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>480</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7591,20 +7598,18 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>189</v>
+        <v>476</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7628,13 +7633,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>485</v>
+        <v>81</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7652,7 +7657,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7670,28 +7675,28 @@
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>81</v>
+        <v>483</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7707,19 +7712,23 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>490</v>
+        <v>189</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>50</v>
+        <v>484</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>485</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7743,13 +7752,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>81</v>
+        <v>489</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7767,7 +7776,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7782,27 +7791,27 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>492</v>
+        <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>343</v>
+        <v>480</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7813,7 +7822,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -7822,16 +7831,16 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>165</v>
+        <v>493</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>496</v>
+        <v>50</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7882,13 +7891,13 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
@@ -7897,27 +7906,27 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>81</v>
+        <v>495</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>343</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>81</v>
+        <v>497</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7928,7 +7937,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -7937,20 +7946,18 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L52" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>503</v>
-      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7999,13 +8006,13 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
@@ -8014,23 +8021,140 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="M53" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AM53" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO52">
+  <autoFilter ref="A1:AO53">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8040,7 +8164,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI51">
+  <conditionalFormatting sqref="A2:AI52">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-donor-order.xlsx
+++ b/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-donor-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:51:12+00:00</t>
+    <t>2026-09-03T16:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
